--- a/outputs/157-4.xlsx
+++ b/outputs/157-4.xlsx
@@ -183,24 +183,28 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -461,373 +465,373 @@
   <dimension ref="E13:M31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.11"/>
   </cols>
   <sheetData>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="L13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="4" t="n">
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="E15" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M15" s="4" t="n">
+      <c r="G15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="5" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="4" t="n">
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="4" t="n">
+      <c r="E17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="4" t="n">
+      <c r="E18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M19" s="4" t="n">
+      <c r="E19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M19" s="5" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M20" s="4" t="n">
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="4" t="n">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5" t="n">
         <v>23</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="4" t="n">
+      <c r="E22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="4" t="n">
+      <c r="E23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="4" t="n">
+      <c r="E24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="4" t="n">
+      <c r="E25" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="4" t="n">
+      <c r="E26" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M27" s="4" t="n">
+      <c r="E27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M27" s="5" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M28" s="4" t="n">
+      <c r="E28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M28" s="5" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="4" t="n">
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="4" t="n">
+      <c r="E30" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="4" t="n">
+      <c r="G31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5" t="n">
         <v>37</v>
       </c>
     </row>

--- a/outputs/157-4.xlsx
+++ b/outputs/157-4.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="13">
   <si>
     <t xml:space="preserve">Employes.</t>
   </si>
@@ -462,7 +462,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E13:M31"/>
+  <dimension ref="E13:M67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.56"/>
@@ -520,48 +520,44 @@
       <c r="E15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
       <c r="M15" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="4"/>
+      <c r="H16" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="I16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="M16" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -570,15 +566,13 @@
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="H17" s="4"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -586,16 +580,18 @@
         <v>9</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="G18" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="I18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -608,55 +604,43 @@
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
-      <c r="L19" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="L19" s="4"/>
       <c r="M19" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
       <c r="M20" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="5" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -664,16 +648,16 @@
         <v>9</v>
       </c>
       <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="G22" s="4"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
+      <c r="L22" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="M22" s="5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -682,15 +666,13 @@
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -700,14 +682,12 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="5" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -718,13 +698,11 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="5" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -736,12 +714,10 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="5" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -754,11 +730,9 @@
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
-      <c r="L27" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="L27" s="4"/>
       <c r="M27" s="5" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -771,30 +745,36 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
-      <c r="L28" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="L28" s="4"/>
       <c r="M28" s="5" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F29" s="4"/>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="J29" s="4" t="s">
         <v>12</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="4"/>
+      <c r="L29" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="M29" s="5" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -803,36 +783,596 @@
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="5" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E33" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L41" s="4"/>
+      <c r="M41" s="5" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M42" s="5" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E44" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="5" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E45" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E46" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="5" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="5" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E48" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="L48" s="4"/>
+      <c r="M48" s="5" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E49" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="5" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E50" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="5" t="n">
         <v>37</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E51" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E52" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="5" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="5" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="5" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="5" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="5" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="5" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E63" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E64" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="5" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="5" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="5" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E67" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="5" t="n">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
